--- a/artfynd/A 45460-2025 artfynd.xlsx
+++ b/artfynd/A 45460-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>65769433</v>
       </c>
       <c r="B2" t="n">
-        <v>99398</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102153</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>630001.4578098528</v>
+        <v>630001</v>
       </c>
       <c r="R2" t="n">
-        <v>6687626.74565373</v>
+        <v>6687627</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -748,19 +743,9 @@
           <t>2003-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2003-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">

--- a/artfynd/A 45460-2025 artfynd.xlsx
+++ b/artfynd/A 45460-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>65769433</v>
       </c>
       <c r="B2" t="n">
-        <v>102153</v>
+        <v>102154</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 45460-2025 artfynd.xlsx
+++ b/artfynd/A 45460-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>65769433</v>
       </c>
       <c r="B2" t="n">
-        <v>102154</v>
+        <v>102155</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 45460-2025 artfynd.xlsx
+++ b/artfynd/A 45460-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>65769433</v>
       </c>
       <c r="B2" t="n">
-        <v>102155</v>
+        <v>102157</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 45460-2025 artfynd.xlsx
+++ b/artfynd/A 45460-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>65769433</v>
       </c>
       <c r="B2" t="n">
-        <v>102157</v>
+        <v>102158</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 45460-2025 artfynd.xlsx
+++ b/artfynd/A 45460-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>65769433</v>
       </c>
       <c r="B2" t="n">
-        <v>102158</v>
+        <v>102164</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 45460-2025 artfynd.xlsx
+++ b/artfynd/A 45460-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>65769433</v>
       </c>
       <c r="B2" t="n">
-        <v>102164</v>
+        <v>102167</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 45460-2025 artfynd.xlsx
+++ b/artfynd/A 45460-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>65769433</v>
       </c>
       <c r="B2" t="n">
-        <v>102167</v>
+        <v>102172</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 45460-2025 artfynd.xlsx
+++ b/artfynd/A 45460-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>65769433</v>
       </c>
       <c r="B2" t="n">
-        <v>102172</v>
+        <v>102175</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
